--- a/diseases/d049/2015-2019.xlsx
+++ b/diseases/d049/2015-2019.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1801,9 +1798,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2689,9 +2683,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -3577,9 +3568,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -4613,9 +4601,6 @@
       <c r="O28" t="n">
         <v>18</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.03530525507051377</v>
       </c>
@@ -5501,9 +5486,6 @@
       <c r="O34" t="n">
         <v>164</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.3216701017535699</v>
       </c>
@@ -6389,9 +6371,6 @@
       <c r="O40" t="n">
         <v>3</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.005884209178418961</v>
       </c>
@@ -7425,9 +7404,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -8313,9 +8289,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -9201,9 +9174,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -10237,9 +10207,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -11125,9 +11092,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -12161,9 +12125,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -13049,9 +13010,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -13937,9 +13895,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -14973,9 +14928,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -15861,9 +15813,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -16749,9 +16698,6 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
@@ -17785,9 +17731,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -18673,9 +18616,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -19561,9 +19501,6 @@
       <c r="O129" t="n">
         <v>0</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
@@ -20597,9 +20534,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -21485,9 +21419,6 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
@@ -22373,9 +22304,6 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
@@ -23409,9 +23337,6 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
@@ -24297,9 +24222,6 @@
       <c r="O161" t="n">
         <v>0</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0</v>
       </c>
@@ -25185,9 +25107,6 @@
       <c r="O167" t="n">
         <v>0</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0</v>
       </c>
@@ -26221,9 +26140,6 @@
       <c r="O174" t="n">
         <v>0</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0</v>
       </c>
@@ -27109,9 +27025,6 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
@@ -27997,9 +27910,6 @@
       <c r="O186" t="n">
         <v>0</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0</v>
       </c>
@@ -29033,9 +28943,6 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0</v>
       </c>
@@ -29921,9 +29828,6 @@
       <c r="O199" t="n">
         <v>0</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0</v>
       </c>
@@ -30957,9 +30861,6 @@
       <c r="O206" t="n">
         <v>0</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0</v>
       </c>
@@ -31845,9 +31746,6 @@
       <c r="O212" t="n">
         <v>0</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0</v>
       </c>
@@ -32733,9 +32631,6 @@
       <c r="O218" t="n">
         <v>0</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0</v>
       </c>
@@ -33769,9 +33664,6 @@
       <c r="O225" t="n">
         <v>0</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0</v>
       </c>
@@ -34657,9 +34549,6 @@
       <c r="O231" t="n">
         <v>0</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0</v>
       </c>
@@ -35545,9 +35434,6 @@
       <c r="O237" t="n">
         <v>0</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="R237" t="n">
         <v>0</v>
       </c>
@@ -36433,9 +36319,6 @@
       <c r="O243" t="n">
         <v>0</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0</v>
       </c>
@@ -37469,9 +37352,6 @@
       <c r="O250" t="n">
         <v>0</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>0</v>
       </c>
@@ -38357,9 +38237,6 @@
       <c r="O256" t="n">
         <v>0</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>0</v>
       </c>
@@ -39393,9 +39270,6 @@
       <c r="O263" t="n">
         <v>0</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>0</v>
       </c>
@@ -40281,9 +40155,6 @@
       <c r="O269" t="n">
         <v>0</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="R269" t="n">
         <v>0</v>
       </c>
@@ -41169,9 +41040,6 @@
       <c r="O275" t="n">
         <v>0</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0</v>
       </c>
@@ -42205,9 +42073,6 @@
       <c r="O282" t="n">
         <v>1</v>
       </c>
-      <c r="Q282" t="n">
-        <v>0</v>
-      </c>
       <c r="R282" t="n">
         <v>0.00193644982211191</v>
       </c>
@@ -43093,9 +42958,6 @@
       <c r="O288" t="n">
         <v>0</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="R288" t="n">
         <v>0</v>
       </c>
@@ -43981,9 +43843,6 @@
       <c r="O294" t="n">
         <v>0</v>
       </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
       <c r="R294" t="n">
         <v>0</v>
       </c>
@@ -45017,9 +44876,6 @@
       <c r="O301" t="n">
         <v>0</v>
       </c>
-      <c r="Q301" t="n">
-        <v>0</v>
-      </c>
       <c r="R301" t="n">
         <v>0</v>
       </c>
@@ -45905,9 +45761,6 @@
       <c r="O307" t="n">
         <v>0</v>
       </c>
-      <c r="Q307" t="n">
-        <v>0</v>
-      </c>
       <c r="R307" t="n">
         <v>0</v>
       </c>
@@ -46941,9 +46794,6 @@
       <c r="O314" t="n">
         <v>0</v>
       </c>
-      <c r="Q314" t="n">
-        <v>0</v>
-      </c>
       <c r="R314" t="n">
         <v>0</v>
       </c>
@@ -47829,9 +47679,6 @@
       <c r="O320" t="n">
         <v>0</v>
       </c>
-      <c r="Q320" t="n">
-        <v>0</v>
-      </c>
       <c r="R320" t="n">
         <v>0</v>
       </c>
@@ -48717,9 +48564,6 @@
       <c r="O326" t="n">
         <v>0</v>
       </c>
-      <c r="Q326" t="n">
-        <v>0</v>
-      </c>
       <c r="R326" t="n">
         <v>0</v>
       </c>
@@ -49605,9 +49449,6 @@
       <c r="O332" t="n">
         <v>0</v>
       </c>
-      <c r="Q332" t="n">
-        <v>0</v>
-      </c>
       <c r="R332" t="n">
         <v>0</v>
       </c>
@@ -50641,9 +50482,6 @@
       <c r="O339" t="n">
         <v>0</v>
       </c>
-      <c r="Q339" t="n">
-        <v>0</v>
-      </c>
       <c r="R339" t="n">
         <v>0</v>
       </c>
@@ -51529,9 +51367,6 @@
       <c r="O345" t="n">
         <v>0</v>
       </c>
-      <c r="Q345" t="n">
-        <v>0</v>
-      </c>
       <c r="R345" t="n">
         <v>0</v>
       </c>
@@ -52417,9 +52252,6 @@
       <c r="O351" t="n">
         <v>0</v>
       </c>
-      <c r="Q351" t="n">
-        <v>0</v>
-      </c>
       <c r="R351" t="n">
         <v>0</v>
       </c>
@@ -53453,9 +53285,6 @@
       <c r="O358" t="n">
         <v>0</v>
       </c>
-      <c r="Q358" t="n">
-        <v>0</v>
-      </c>
       <c r="R358" t="n">
         <v>0</v>
       </c>
@@ -54341,9 +54170,6 @@
       <c r="O364" t="n">
         <v>0</v>
       </c>
-      <c r="Q364" t="n">
-        <v>0</v>
-      </c>
       <c r="R364" t="n">
         <v>0</v>
       </c>
@@ -55377,9 +55203,6 @@
       <c r="O371" t="n">
         <v>0</v>
       </c>
-      <c r="Q371" t="n">
-        <v>0</v>
-      </c>
       <c r="R371" t="n">
         <v>0</v>
       </c>
@@ -56263,9 +56086,6 @@
         <v>0</v>
       </c>
       <c r="O377" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q377" t="n">
         <v>0</v>
       </c>
       <c r="R377" t="n">
